--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_226_Equatorial_Guinea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_226_Equatorial_Guinea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R5527d251e3274a5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R577096d8fd514eb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R7c4c2755b10e4a5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R463ba78cdd604a24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R2e81db58958b40a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rc466c79c020e4d4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R534db1262ab44d74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R2770133c5a05494b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R98acc4e856d94082"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd256df298d754f76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R3947fd72092c41c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R25ea0bb525c7406a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ226CommercialTable" displayName="EEZ226CommercialTable" ref="A1:O9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O9"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ226CommercialTable" displayName="EEZ226CommercialTable" ref="A1:E9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E9"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ226FunctionalTable" displayName="EEZ226FunctionalTable" ref="A1:O18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O18"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ226FunctionalTable" displayName="EEZ226FunctionalTable" ref="A1:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E18"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ226ValidationTable" displayName="EEZ226ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ226ValidationTable" displayName="EEZ226ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5116,7 +5070,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R464570180e8a485e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ff69c657bb54a2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5126,20 +5080,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5147,498 +5091,174 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>70</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>3162.2776601683795</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$67,A2,'Species'!$U$2:$U$67))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>221359.43621178655</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>221359.43621178655</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>38.244854757300004</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.9073937051381535</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>80.79671525546404</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>38.244854757300004</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>110.61760402236372</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$67,A3,'Species'!$U$2:$U$67))</x:f>
-        <x:v>4230.5541994358255</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.9073937051381535</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>80.79671525546404</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3090.0586398121477</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1140.4955596236778</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.3690854098785035</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.3690854098785036</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>164.7878279586</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.551154895299147</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>355.75818051715027</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>164.7878279586</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>358.7521042630246</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$67,A4,'Species'!$U$2:$U$67))</x:f>
-        <x:v>59117.980037081026</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.551154895299147</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>355.75818051715027</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>58624.61784592472</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>493.36219115630956</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0084156146220509</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.00841561462205089</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>32.1658234322</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3541241501131354</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>226.0081758867061</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>32.1658234322</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>311.6989936977853</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$67,A5,'Species'!$U$2:$U$67))</x:f>
-        <x:v>10026.054795277381</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3541241501131354</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>226.0081758867061</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>7269.73907980539</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>2756.315715471991</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.3791491943815097</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.3791491943815097</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>14079.809008529699</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.283796492720531</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>192.2190793020899</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>14079.809008529699</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>198.8684545961869</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$67,A6,'Species'!$U$2:$U$67))</x:f>
-        <x:v>2800029.8585357717</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.283796492720531</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>192.2190793020899</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2706407.92436885</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>93621.93416692177</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0345926914135661</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.034592691413566176</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>5903.4041785493</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.577115006838783</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>377.6721902022821</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>5903.4041785493</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>660.605655094716</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$67,A7,'Species'!$U$2:$U$67))</x:f>
-        <x:v>3899822.1846594443</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.577115006838783</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>377.6721902022821</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2229551.585762018</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1670270.5988974264</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.749150909790033</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.749150909790033</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>396.4425438478</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.682348836355115</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>481.2257259768299</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>396.4425438478</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>679.6002825526876</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$67,A8,'Species'!$U$2:$U$67))</x:f>
-        <x:v>269422.46481487114</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.682348836355115</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>481.2257259768299</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>190778.35097125877</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>78644.11384361237</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4122276633760207</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.4122276633760206</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2409.3382904826003</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.42795402222293</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2678.884702325946</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2409.3382904826003</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2685.2057224427936</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$67,A9,'Species'!$U$2:$U$67))</x:f>
-        <x:v>6469568.964904416</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.42795402222293</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2678.884702325946</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>6454339.489101985</x:v>
       </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>15229.475802431814</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0023595715453373</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0023595715453372823</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G9">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O9">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2def2b510cd34db7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R901b1329bf924291"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5648,20 +5268,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5669,984 +5279,345 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>33.8743706752</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.009278021534348</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1021.5932659836401</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>33.8743706752</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1135.0310180382048</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$67,A2,'Species'!$U$2:$U$67))</x:f>
-        <x:v>38448.46143287577</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.009278021534348</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1021.5932659836401</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>34605.82897121801</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>3842.632461657755</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1110400350430474</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.11104003504304745</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>25</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.42</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2630.2679918953813</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2630.2679918953813</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$67,A3,'Species'!$U$2:$U$67))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>65756.69979738453</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.42</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2630.2679918953813</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>65756.69979738453</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>360.99073223930003</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.866320033784777</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>735.0553345955153</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>360.99073223930003</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>776.3869931380731</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$67,A4,'Species'!$U$2:$U$67))</x:f>
-        <x:v>280268.5091539814</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.866320033784777</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>735.0553345955153</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>265348.16347203875</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>14920.34568194265</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0562293158042335</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.05622931580423353</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2812.6988548316003</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.42281832417489</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2647.3924390159914</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2812.6988548316003</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2654.331341498395</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$67,A5,'Species'!$U$2:$U$67))</x:f>
-        <x:v>7465834.724576161</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.42281832417489</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2647.3924390159914</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>7446317.681510116</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>19517.04306604527</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0026210328246548</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.002621032824654777</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>298.7976423784</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.511674669461683</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>324.84386527434384</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>298.7976423784</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>337.5688941828674</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$67,A6,'Species'!$U$2:$U$67))</x:f>
-        <x:v>100864.78972212435</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.511674669461683</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>324.84386527434384</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>97062.58108506053</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>3802.2086370638135</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0391727542638884</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.039172754263888346</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>15.214031619</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>316.22776601683796</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>15.214031619</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$67,A7,'Species'!$U$2:$U$67))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>4811.099230985907</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.5</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>4811.099230985907</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>97.6449014694</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.204619204958401</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1601.8402604195587</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>97.6449014694</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1726.2311964702988</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$67,A8,'Species'!$U$2:$U$67))</x:f>
-        <x:v>168557.6750927468</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.204619204958401</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1601.8402604195587</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>156411.53439838585</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>12146.140694360947</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0776550191204204</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0776550191204204</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>22.071196829399998</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>2.612365911990076</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>40.960562493978195</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>22.071196829399998</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>42.060115591439015</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$67,A9,'Species'!$U$2:$U$67))</x:f>
-        <x:v>928.3170898859662</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>2.612365911990076</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>40.960562493978195</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>904.048637047532</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>24.2684528384342</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0268441893985825</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.02684418939858237</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>70</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>3162.2776601683795</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$67,A10,'Species'!$U$2:$U$67))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>221359.43621178655</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>221359.43621178655</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>369.669809464</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.3451515838368846</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>221.38672912374335</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>369.669809464</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>372.33204115014877</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$67,A11,'Species'!$U$2:$U$67))</x:f>
-        <x:v>137639.9147093177</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.3451515838368846</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>221.38672912374335</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>81839.9899730324</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>55799.924736285306</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.681817345709259</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.6818173457092588</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>11098.9032137207</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.337127414612677</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>217.33387059423777</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>11098.9032137207</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>243.62593953194911</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$67,A12,'Species'!$U$2:$U$67))</x:f>
-        <x:v>2703980.723216875</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.337127414612677</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>217.33387059423777</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>2412167.594788744</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>291813.1284281309</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1209754782621926</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.1209754782621925</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>560.9943663649999</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.821112384708391</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>662.3878911865512</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>560.9943663649999</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>863.0254488083981</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$67,A13,'Species'!$U$2:$U$67))</x:f>
-        <x:v>484152.41481113696</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.821112384708391</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>662.3878911865512</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>371595.8753040478</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>112556.53950708918</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.3029004006435567</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.3029004006435566</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1017.1895049463001</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.006834028126748</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1015.8603930400612</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1017.1895049463001</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1016.875267864747</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$67,A14,'Species'!$U$2:$U$67))</x:f>
-        <x:v>1034354.8503114783</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.006834028126748</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1015.8603930400612</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1033322.5302909737</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>1032.3200205045287</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.000999029819096</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.0009990298190961124</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>16.173657927900003</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>16.173657927900003</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$67,A15,'Species'!$U$2:$U$67))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>3302.2371095498593</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>3302.2371095498593</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>2130.1824171325998</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.0696901879481358</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>117.40597187797636</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>2130.1824171325998</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>126.31750782975155</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$67,A16,'Species'!$U$2:$U$67))</x:f>
-        <x:v>269079.33415494626</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.0696901879481358</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>117.40597187797636</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>250096.1369608297</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>18983.19719411657</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0759036002107052</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.07590360021070512</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>4000.0000000001</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.24</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>173.78008287493762</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>4000.0000000001</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$67,A17,'Species'!$U$2:$U$67))</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>695120.3314997678</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.24</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
-        <x:v>695120.3314997678</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>164.7878279586</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.551154895299147</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>355.75818051715027</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>164.7878279586</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>358.7521042630246</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$67,A18,'Species'!$U$2:$U$67))</x:f>
-        <x:v>59117.980037081026</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.551154895299147</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>355.75818051715027</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>58624.61784592472</x:v>
       </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>493.36219115630956</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0084156146220509</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.00841561462205089</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G18">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O18">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1a4cd91179b4df9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3362a96f85444273"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6821,7 +5792,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6920,7 +5891,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>13733577.498158084</x:v>
+        <x:v>11871421.201981438</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6934,7 +5905,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>13733577.498158084</x:v>
+        <x:v>13198646.387086893</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6948,7 +5919,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.862645149230957e-9</x:v>
+        <x:v>-1862156.2961766478</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6962,7 +5933,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-1.862645149230957e-9</x:v>
+        <x:v>-534931.1110711936</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6973,9 +5944,9 @@
         <x:v>EEZ_226</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6987,47 +5958,19 @@
         <x:v>EEZ_226</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_226</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_226</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd25886d150694fee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97d3b3115c0e4bbd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7074,7 +6017,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
